--- a/program.xlsx
+++ b/program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marco/work/git/rt2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E5D9F-EBB0-5D40-9E07-5BFD022C6DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32E4036-A812-EF49-9111-55204EDC53A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29380" yWindow="-6060" windowWidth="19220" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
+        <v>134</v>
+      </c>
+      <c r="B2">
         <v>58457</v>
-      </c>
-      <c r="B2">
-        <v>134</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>58513</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
+        <v>183</v>
+      </c>
+      <c r="B4">
         <v>58474</v>
-      </c>
-      <c r="B4">
-        <v>183</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
+        <v>186</v>
+      </c>
+      <c r="B5">
         <v>58476</v>
-      </c>
-      <c r="B5">
-        <v>186</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
+        <v>103</v>
+      </c>
+      <c r="B6">
         <v>58528</v>
-      </c>
-      <c r="B6">
-        <v>103</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
+        <v>101</v>
+      </c>
+      <c r="B7">
         <v>58503</v>
-      </c>
-      <c r="B7">
-        <v>101</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
+        <v>141</v>
+      </c>
+      <c r="B8">
         <v>58460</v>
-      </c>
-      <c r="B8">
-        <v>141</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
+        <v>86</v>
+      </c>
+      <c r="B9">
         <v>58437</v>
-      </c>
-      <c r="B9">
-        <v>86</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
+        <v>69</v>
+      </c>
+      <c r="B10">
         <v>58428</v>
-      </c>
-      <c r="B10">
-        <v>69</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
+        <v>85</v>
+      </c>
+      <c r="B11">
         <v>58436</v>
-      </c>
-      <c r="B11">
-        <v>85</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>65</v>
+      </c>
+      <c r="B12">
         <v>58495</v>
-      </c>
-      <c r="B12">
-        <v>65</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
+        <v>108</v>
+      </c>
+      <c r="B13">
         <v>58447</v>
-      </c>
-      <c r="B13">
-        <v>108</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
         <v>58478</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
+        <v>165</v>
+      </c>
+      <c r="B15">
         <v>58468</v>
-      </c>
-      <c r="B15">
-        <v>165</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
+        <v>70</v>
+      </c>
+      <c r="B16">
         <v>58429</v>
-      </c>
-      <c r="B16">
-        <v>70</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>129</v>
+      </c>
+      <c r="B17">
         <v>58516</v>
-      </c>
-      <c r="B17">
-        <v>129</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>42</v>
+      </c>
+      <c r="B18">
         <v>58421</v>
-      </c>
-      <c r="B18">
-        <v>42</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
+        <v>23</v>
+      </c>
+      <c r="B19">
         <v>58519</v>
-      </c>
-      <c r="B19">
-        <v>23</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20">
         <v>58481</v>
-      </c>
-      <c r="B20">
-        <v>7</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
+        <v>88</v>
+      </c>
+      <c r="B21">
         <v>58499</v>
-      </c>
-      <c r="B21">
-        <v>88</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
+        <v>115</v>
+      </c>
+      <c r="B22">
         <v>58450</v>
-      </c>
-      <c r="B22">
-        <v>115</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
+        <v>118</v>
+      </c>
+      <c r="B23">
         <v>58505</v>
-      </c>
-      <c r="B23">
-        <v>118</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
+        <v>112</v>
+      </c>
+      <c r="B24">
         <v>58449</v>
-      </c>
-      <c r="B24">
-        <v>112</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
+        <v>96</v>
+      </c>
+      <c r="B25">
         <v>58441</v>
-      </c>
-      <c r="B25">
-        <v>96</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
+        <v>41</v>
+      </c>
+      <c r="B26">
         <v>58420</v>
-      </c>
-      <c r="B26">
-        <v>41</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
+        <v>123</v>
+      </c>
+      <c r="B27">
         <v>58515</v>
-      </c>
-      <c r="B27">
-        <v>123</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28">
         <v>58482</v>
-      </c>
-      <c r="B28">
-        <v>9</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
+        <v>31</v>
+      </c>
+      <c r="B29">
         <v>58485</v>
-      </c>
-      <c r="B29">
-        <v>31</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
+        <v>10</v>
+      </c>
+      <c r="B30">
         <v>58406</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
+        <v>157</v>
+      </c>
+      <c r="B31">
         <v>58467</v>
-      </c>
-      <c r="B31">
-        <v>157</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
+        <v>87</v>
+      </c>
+      <c r="B32">
         <v>58497</v>
-      </c>
-      <c r="B32">
-        <v>87</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
+        <v>59</v>
+      </c>
+      <c r="B33">
         <v>58425</v>
-      </c>
-      <c r="B33">
-        <v>59</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
+        <v>185</v>
+      </c>
+      <c r="B34">
         <v>58475</v>
-      </c>
-      <c r="B34">
-        <v>185</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
+        <v>36</v>
+      </c>
+      <c r="B35">
         <v>58523</v>
-      </c>
-      <c r="B35">
-        <v>36</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
+        <v>56</v>
+      </c>
+      <c r="B36">
         <v>58492</v>
-      </c>
-      <c r="B36">
-        <v>56</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
+        <v>12</v>
+      </c>
+      <c r="B37">
         <v>58407</v>
-      </c>
-      <c r="B37">
-        <v>12</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38">
+        <v>145</v>
+      </c>
+      <c r="B38">
         <v>58462</v>
-      </c>
-      <c r="B38">
-        <v>145</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39">
+        <v>22</v>
+      </c>
+      <c r="B39">
         <v>58412</v>
-      </c>
-      <c r="B39">
-        <v>22</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40">
+        <v>76</v>
+      </c>
+      <c r="B40">
         <v>58433</v>
-      </c>
-      <c r="B40">
-        <v>76</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41">
+        <v>106</v>
+      </c>
+      <c r="B41">
         <v>58446</v>
-      </c>
-      <c r="B41">
-        <v>106</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42">
+        <v>26</v>
+      </c>
+      <c r="B42">
         <v>58414</v>
-      </c>
-      <c r="B42">
-        <v>26</v>
       </c>
       <c r="C42">
         <v>4</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
+        <v>117</v>
+      </c>
+      <c r="B43">
         <v>58451</v>
-      </c>
-      <c r="B43">
-        <v>117</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44">
+        <v>98</v>
+      </c>
+      <c r="B44">
         <v>58442</v>
-      </c>
-      <c r="B44">
-        <v>98</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45">
+        <v>14</v>
+      </c>
+      <c r="B45">
         <v>58410</v>
-      </c>
-      <c r="B45">
-        <v>14</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46">
+        <v>93</v>
+      </c>
+      <c r="B46">
         <v>58439</v>
-      </c>
-      <c r="B46">
-        <v>93</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47">
+        <v>2</v>
+      </c>
+      <c r="B47">
         <v>58479</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48">
+        <v>110</v>
+      </c>
+      <c r="B48">
         <v>58448</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
         <v>58422</v>
-      </c>
-      <c r="B49">
-        <v>46</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
+        <v>148</v>
+      </c>
+      <c r="B50">
         <v>58465</v>
-      </c>
-      <c r="B50">
-        <v>148</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51">
+        <v>131</v>
+      </c>
+      <c r="B51">
         <v>58456</v>
-      </c>
-      <c r="B51">
-        <v>131</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
+        <v>104</v>
+      </c>
+      <c r="B52">
         <v>58445</v>
-      </c>
-      <c r="B52">
-        <v>104</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
+        <v>154</v>
+      </c>
+      <c r="B53">
         <v>58466</v>
-      </c>
-      <c r="B53">
-        <v>154</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
+        <v>75</v>
+      </c>
+      <c r="B54">
         <v>58432</v>
-      </c>
-      <c r="B54">
-        <v>75</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
+        <v>187</v>
+      </c>
+      <c r="B55">
         <v>58477</v>
-      </c>
-      <c r="B55">
-        <v>187</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
+        <v>82</v>
+      </c>
+      <c r="B56">
         <v>58498</v>
-      </c>
-      <c r="B56">
-        <v>82</v>
       </c>
       <c r="C56">
         <v>5</v>
@@ -2876,10 +2876,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57">
+        <v>28</v>
+      </c>
+      <c r="B57">
         <v>58415</v>
-      </c>
-      <c r="B57">
-        <v>28</v>
       </c>
       <c r="C57">
         <v>5</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58">
+        <v>74</v>
+      </c>
+      <c r="B58">
         <v>58431</v>
-      </c>
-      <c r="B58">
-        <v>74</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59">
+        <v>95</v>
+      </c>
+      <c r="B59">
         <v>58501</v>
-      </c>
-      <c r="B59">
-        <v>95</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
         <v>58493</v>
-      </c>
-      <c r="B60">
-        <v>57</v>
       </c>
       <c r="C60">
         <v>6</v>
@@ -2965,10 +2965,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61">
+        <v>169</v>
+      </c>
+      <c r="B61">
         <v>58471</v>
-      </c>
-      <c r="B61">
-        <v>169</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2985,10 +2985,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62">
+        <v>77</v>
+      </c>
+      <c r="B62">
         <v>58514</v>
-      </c>
-      <c r="B62">
-        <v>77</v>
       </c>
       <c r="C62">
         <v>6</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2">
         <v>58486</v>
-      </c>
-      <c r="B2">
-        <v>32</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3067,10 +3067,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
+        <v>58</v>
+      </c>
+      <c r="B3">
         <v>58494</v>
-      </c>
-      <c r="B3">
-        <v>58</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
+        <v>92</v>
+      </c>
+      <c r="B4">
         <v>58500</v>
-      </c>
-      <c r="B4">
-        <v>92</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
+        <v>47</v>
+      </c>
+      <c r="B5">
         <v>58423</v>
-      </c>
-      <c r="B5">
-        <v>47</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
+        <v>102</v>
+      </c>
+      <c r="B6">
         <v>58444</v>
-      </c>
-      <c r="B6">
-        <v>102</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
+        <v>67</v>
+      </c>
+      <c r="B7">
         <v>58496</v>
-      </c>
-      <c r="B7">
-        <v>67</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3176,10 +3176,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
+        <v>147</v>
+      </c>
+      <c r="B8">
         <v>58464</v>
-      </c>
-      <c r="B8">
-        <v>147</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
+        <v>61</v>
+      </c>
+      <c r="B9">
         <v>58426</v>
-      </c>
-      <c r="B9">
-        <v>61</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
+        <v>125</v>
+      </c>
+      <c r="B10">
         <v>58454</v>
-      </c>
-      <c r="B10">
-        <v>125</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
+        <v>45</v>
+      </c>
+      <c r="B11">
         <v>58490</v>
-      </c>
-      <c r="B11">
-        <v>45</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>146</v>
+      </c>
+      <c r="B12">
         <v>58463</v>
-      </c>
-      <c r="B12">
-        <v>146</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -3288,10 +3288,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
+        <v>189</v>
+      </c>
+      <c r="B13">
         <v>58524</v>
-      </c>
-      <c r="B13">
-        <v>189</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
+        <v>124</v>
+      </c>
+      <c r="B14">
         <v>58453</v>
-      </c>
-      <c r="B14">
-        <v>124</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
+        <v>44</v>
+      </c>
+      <c r="B15">
         <v>58489</v>
-      </c>
-      <c r="B15">
-        <v>44</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
+        <v>190</v>
+      </c>
+      <c r="B16">
         <v>58525</v>
-      </c>
-      <c r="B16">
-        <v>190</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -3380,10 +3380,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>140</v>
+      </c>
+      <c r="B17">
         <v>58522</v>
-      </c>
-      <c r="B17">
-        <v>140</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>166</v>
+      </c>
+      <c r="B18">
         <v>58469</v>
-      </c>
-      <c r="B18">
-        <v>166</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
+        <v>170</v>
+      </c>
+      <c r="B19">
         <v>58510</v>
-      </c>
-      <c r="B19">
-        <v>170</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
+        <v>83</v>
+      </c>
+      <c r="B20">
         <v>58435</v>
-      </c>
-      <c r="B20">
-        <v>83</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
+        <v>168</v>
+      </c>
+      <c r="B21">
         <v>58512</v>
-      </c>
-      <c r="B21">
-        <v>168</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
+        <v>128</v>
+      </c>
+      <c r="B22">
         <v>58507</v>
-      </c>
-      <c r="B22">
-        <v>128</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
+        <v>161</v>
+      </c>
+      <c r="B23">
         <v>58509</v>
-      </c>
-      <c r="B23">
-        <v>161</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
+        <v>13</v>
+      </c>
+      <c r="B24">
         <v>58408</v>
-      </c>
-      <c r="B24">
-        <v>13</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
+        <v>99</v>
+      </c>
+      <c r="B25">
         <v>58443</v>
-      </c>
-      <c r="B25">
-        <v>99</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
+        <v>91</v>
+      </c>
+      <c r="B26">
         <v>58438</v>
-      </c>
-      <c r="B26">
-        <v>91</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
         <v>58413</v>
-      </c>
-      <c r="B27">
-        <v>25</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
+        <v>50</v>
+      </c>
+      <c r="B28">
         <v>58491</v>
-      </c>
-      <c r="B28">
-        <v>50</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -3650,10 +3650,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
+        <v>144</v>
+      </c>
+      <c r="B29">
         <v>58461</v>
-      </c>
-      <c r="B29">
-        <v>144</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
+        <v>139</v>
+      </c>
+      <c r="B30">
         <v>58459</v>
-      </c>
-      <c r="B30">
-        <v>139</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
+        <v>193</v>
+      </c>
+      <c r="B31">
         <v>58527</v>
-      </c>
-      <c r="B31">
-        <v>193</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3719,10 +3719,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
+        <v>167</v>
+      </c>
+      <c r="B32">
         <v>58470</v>
-      </c>
-      <c r="B32">
-        <v>167</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
+        <v>138</v>
+      </c>
+      <c r="B33">
         <v>58458</v>
-      </c>
-      <c r="B33">
-        <v>138</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
+        <v>37</v>
+      </c>
+      <c r="B34">
         <v>58417</v>
-      </c>
-      <c r="B34">
-        <v>37</v>
       </c>
       <c r="C34">
         <v>4</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
+        <v>6</v>
+      </c>
+      <c r="B35">
         <v>58405</v>
-      </c>
-      <c r="B35">
-        <v>6</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
+        <v>180</v>
+      </c>
+      <c r="B36">
         <v>58473</v>
-      </c>
-      <c r="B36">
-        <v>180</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
+        <v>132</v>
+      </c>
+      <c r="B37">
         <v>58508</v>
-      </c>
-      <c r="B37">
-        <v>132</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38">
+        <v>52</v>
+      </c>
+      <c r="B38">
         <v>58424</v>
-      </c>
-      <c r="B38">
-        <v>52</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39">
+        <v>142</v>
+      </c>
+      <c r="B39">
         <v>58530</v>
-      </c>
-      <c r="B39">
-        <v>142</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40">
+        <v>194</v>
+      </c>
+      <c r="B40">
         <v>58531</v>
-      </c>
-      <c r="B40">
-        <v>194</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41">
+        <v>71</v>
+      </c>
+      <c r="B41">
         <v>58430</v>
-      </c>
-      <c r="B41">
-        <v>71</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42">
+        <v>29</v>
+      </c>
+      <c r="B42">
         <v>58416</v>
-      </c>
-      <c r="B42">
-        <v>29</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
+        <v>121</v>
+      </c>
+      <c r="B43">
         <v>58452</v>
-      </c>
-      <c r="B43">
-        <v>121</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44">
+        <v>94</v>
+      </c>
+      <c r="B44">
         <v>58440</v>
-      </c>
-      <c r="B44">
-        <v>94</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45">
         <v>58480</v>
-      </c>
-      <c r="B45">
-        <v>4</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46">
+        <v>15</v>
+      </c>
+      <c r="B46">
         <v>58409</v>
-      </c>
-      <c r="B46">
-        <v>15</v>
       </c>
       <c r="C46">
         <v>6</v>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47">
+        <v>62</v>
+      </c>
+      <c r="B47">
         <v>58427</v>
-      </c>
-      <c r="B47">
-        <v>62</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4078,10 +4078,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48">
+        <v>100</v>
+      </c>
+      <c r="B48">
         <v>58502</v>
-      </c>
-      <c r="B48">
-        <v>100</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
+        <v>40</v>
+      </c>
+      <c r="B49">
         <v>58518</v>
-      </c>
-      <c r="B49">
-        <v>40</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
+        <v>34</v>
+      </c>
+      <c r="B50">
         <v>58487</v>
-      </c>
-      <c r="B50">
-        <v>34</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51">
+        <v>105</v>
+      </c>
+      <c r="B51">
         <v>58504</v>
-      </c>
-      <c r="B51">
-        <v>105</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
+        <v>130</v>
+      </c>
+      <c r="B52">
         <v>58455</v>
-      </c>
-      <c r="B52">
-        <v>130</v>
       </c>
       <c r="C52">
         <v>6</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
+        <v>80</v>
+      </c>
+      <c r="B53">
         <v>58521</v>
-      </c>
-      <c r="B53">
-        <v>80</v>
       </c>
       <c r="C53">
         <v>6</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
+        <v>178</v>
+      </c>
+      <c r="B54">
         <v>58472</v>
-      </c>
-      <c r="B54">
-        <v>178</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
+        <v>43</v>
+      </c>
+      <c r="B55">
         <v>58488</v>
-      </c>
-      <c r="B55">
-        <v>43</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
+        <v>39</v>
+      </c>
+      <c r="B56">
         <v>58419</v>
-      </c>
-      <c r="B56">
-        <v>39</v>
       </c>
       <c r="C56">
         <v>6</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57">
+        <v>122</v>
+      </c>
+      <c r="B57">
         <v>58506</v>
-      </c>
-      <c r="B57">
-        <v>122</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -4302,10 +4302,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58">
+        <v>19</v>
+      </c>
+      <c r="B58">
         <v>58483</v>
-      </c>
-      <c r="B58">
-        <v>19</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59">
+        <v>18</v>
+      </c>
+      <c r="B59">
         <v>58411</v>
-      </c>
-      <c r="B59">
-        <v>18</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
+        <v>38</v>
+      </c>
+      <c r="B60">
         <v>58418</v>
-      </c>
-      <c r="B60">
-        <v>38</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61">
+        <v>79</v>
+      </c>
+      <c r="B61">
         <v>58434</v>
-      </c>
-      <c r="B61">
-        <v>79</v>
       </c>
       <c r="C61">
         <v>7</v>
